--- a/data/AuditLog.xlsx
+++ b/data/AuditLog.xlsx
@@ -1,58 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +279,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,80 +414,391 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Timestamp</v>
-      </c>
-      <c r="B1" t="str">
-        <v>User</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Action</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Row_ID</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Field</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Old_Value</v>
-      </c>
-      <c r="G1" t="str">
-        <v>New_Value</v>
-      </c>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Old_Value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>New_Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:35:05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ItemName</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>bye</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:35:05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:35:26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:37:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ItemName</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:37:44</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>again</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:37:44</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:37:44</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:46:18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:46:28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ItemName</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>youch</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:46:28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-25 13:46:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/AuditLog.xlsx
+++ b/data/AuditLog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,2271 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>16</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>17</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>19</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>21</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>22</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>23</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>24</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>26</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>27</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>28</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>29</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>30</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>31</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>32</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>33</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>34</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>36</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>37</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>38</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>39</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>40</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>41</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>42</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>43</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>44</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>45</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>46</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:48:10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>47</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>48</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DateAdded</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>48</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>48</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>ModelNumber</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>48</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SerialNumber</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>48</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>48</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>48</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>WarrantyExpiration</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>48</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>WarrantyProvider</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:46</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>48</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AlertSent</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AssignedTo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>48</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DateAdded</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>48</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>48</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ModelNumber</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>48</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SerialNumber</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>48</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>48</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>48</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>WarrantyExpiration</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>48</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WarrantyProvider</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>48</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AlertSent</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ItemName</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Cisco Tablet 5</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>wewew</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>ItemID</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ITM0008</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>wewe</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>48</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DateAdded</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>48</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>48</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>ModelNumber</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>48</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SerialNumber</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>48</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>48</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>48</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>WarrantyExpiration</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>48</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>WarrantyProvider</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:08:39</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>changed</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>48</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AlertSent</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
